--- a/Route List.xlsx
+++ b/Route List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9826d72e9687af94/Documents/Game Dev/Climbing Grid Prototype/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{9B4CB477-06CF-444B-B570-B41C50BF9165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6E9FDE8-2C29-44ED-92AC-4626F8E41767}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{9B4CB477-06CF-444B-B570-B41C50BF9165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B600739-9159-4792-A030-273E3841D458}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="70" yWindow="350" windowWidth="19200" windowHeight="11170" xr2:uid="{18AC4EAE-B115-493E-864C-59EBF11DD47A}"/>
+    <workbookView xWindow="2390" yWindow="270" windowWidth="19200" windowHeight="14170" xr2:uid="{18AC4EAE-B115-493E-864C-59EBF11DD47A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -157,6 +157,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -476,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6120AFA6-BFD9-4C15-8114-AEE1065F7BAB}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -564,6 +568,36 @@
         <v>16</v>
       </c>
     </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
